--- a/public/downloads/SainiElectronic2022.xlsx
+++ b/public/downloads/SainiElectronic2022.xlsx
@@ -8,28 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -61,10 +63,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -163,13 +165,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>O</t>
   </si>
   <si>
-    <t>N</t>
+    <t>CH</t>
   </si>
   <si>
-    <t>CH</t>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -655,10 +678,10 @@
         <v>441</v>
       </c>
       <c r="N3" s="5">
-        <v>5904.281548023224</v>
+        <v>5904281.548023224</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03313382276732357</v>
+        <v>33.13382276732357</v>
       </c>
       <c r="P3" s="5">
         <v>178195</v>
@@ -705,10 +728,10 @@
         <v>441</v>
       </c>
       <c r="N4" s="5">
-        <v>4772.790107011795</v>
+        <v>4772790.107011795</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04690195759683764</v>
+        <v>46.90195759683764</v>
       </c>
       <c r="P4" s="5">
         <v>101761</v>
@@ -755,10 +778,10 @@
         <v>441</v>
       </c>
       <c r="N5" s="5">
-        <v>14055.19436073303</v>
+        <v>14055194.36073303</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1286104621927349</v>
+        <v>128.6104621927349</v>
       </c>
       <c r="P5" s="5">
         <v>109285</v>
@@ -805,10 +828,10 @@
         <v>441</v>
       </c>
       <c r="N6" s="5">
-        <v>8386.180981636047</v>
+        <v>8386180.981636047</v>
       </c>
       <c r="O6" s="4">
-        <v>0.0862855715203676</v>
+        <v>86.2855715203676</v>
       </c>
       <c r="P6" s="5">
         <v>97191</v>
@@ -855,10 +878,10 @@
         <v>441</v>
       </c>
       <c r="N7" s="5">
-        <v>19673.90658664703</v>
+        <v>19673906.58664703</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1693559089485752</v>
+        <v>169.3559089485752</v>
       </c>
       <c r="P7" s="5">
         <v>116169</v>
@@ -905,10 +928,10 @@
         <v>441</v>
       </c>
       <c r="N8" s="5">
-        <v>1038.137613534927</v>
+        <v>1038137.613534927</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01274351386544888</v>
+        <v>12.74351386544888</v>
       </c>
       <c r="P8" s="5">
         <v>81464</v>
@@ -955,10 +978,10 @@
         <v>441</v>
       </c>
       <c r="N9" s="5">
-        <v>2843.546705245972</v>
+        <v>2843546.705245972</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03072310980882481</v>
+        <v>30.72310980882481</v>
       </c>
       <c r="P9" s="5">
         <v>92554</v>
@@ -1005,10 +1028,10 @@
         <v>441</v>
       </c>
       <c r="N10" s="5">
-        <v>6981.91864323616</v>
+        <v>6981918.64323616</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09107285970071821</v>
+        <v>91.07285970071821</v>
       </c>
       <c r="P10" s="5">
         <v>76663</v>
@@ -1055,10 +1078,10 @@
         <v>441</v>
       </c>
       <c r="N11" s="5">
-        <v>6722.461027145386</v>
+        <v>6722461.027145386</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03862728562893104</v>
+        <v>38.62728562893104</v>
       </c>
       <c r="P11" s="5">
         <v>174034</v>
@@ -1105,10 +1128,10 @@
         <v>441</v>
       </c>
       <c r="N12" s="5">
-        <v>1718.87504529953</v>
+        <v>1718875.04529953</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01893221845006146</v>
+        <v>18.93221845006146</v>
       </c>
       <c r="P12" s="5">
         <v>90791</v>
@@ -1155,10 +1178,10 @@
         <v>441</v>
       </c>
       <c r="N13" s="5">
-        <v>11677.0212085247</v>
+        <v>11677021.2085247</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07573972880157163</v>
+        <v>75.73972880157163</v>
       </c>
       <c r="P13" s="5">
         <v>154173</v>
@@ -1205,10 +1228,10 @@
         <v>433</v>
       </c>
       <c r="N14" s="5">
-        <v>25842.72315478325</v>
+        <v>25842723.15478325</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2384300991335054</v>
+        <v>238.4300991335054</v>
       </c>
       <c r="P14" s="5">
         <v>108387</v>
@@ -1255,10 +1278,10 @@
         <v>350</v>
       </c>
       <c r="N15" s="5">
-        <v>17141.23529887199</v>
+        <v>17141235.29887199</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2489179283341126</v>
+        <v>248.9179283341126</v>
       </c>
       <c r="P15" s="5">
         <v>68863</v>
@@ -1305,10 +1328,10 @@
         <v>433</v>
       </c>
       <c r="N16" s="5">
-        <v>8895.250411272049</v>
+        <v>8895250.411272049</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09732540905360186</v>
+        <v>97.32540905360186</v>
       </c>
       <c r="P16" s="5">
         <v>91397</v>
@@ -1336,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1347,9 +1370,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1383,8 +1412,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1406,132 +1443,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4778777165825168</v>
+        <v>1.016225177535246</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3468308513950089</v>
+        <v>0.7059060113183256</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2266284745811665</v>
+        <v>1.047774118887867</v>
       </c>
       <c r="E3" s="4">
-        <v>70.80553179355603</v>
+        <v>66.41411055440146</v>
       </c>
       <c r="F3" s="4">
-        <v>77.9445136572491</v>
+        <v>73.1051320178434</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1677176189456047</v>
+      </c>
+      <c r="O3" s="5">
+        <v>121</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.059937190443817</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7872032508665375</v>
+      </c>
+      <c r="R3" s="5">
+        <v>116</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3922117648842332</v>
+        <v>0.7240268212617482</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2928242381625077</v>
+        <v>0.6310667018862659</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2012060830280189</v>
+        <v>0.5277516273496105</v>
       </c>
       <c r="E4" s="4">
-        <v>74.35169556544409</v>
+        <v>72.32622372257148</v>
       </c>
       <c r="F4" s="4">
-        <v>81.9856688701629</v>
+        <v>82.16051874653105</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.6559463275487086</v>
+      </c>
+      <c r="O4" s="5">
+        <v>119</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3012795312585546</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1868434626791098</v>
+      </c>
+      <c r="R4" s="5">
+        <v>118</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3906891263872809</v>
+        <v>0.4467732705209551</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2731464151325319</v>
+        <v>0.3658073156074957</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2743906321625988</v>
+        <v>0.2637966749598041</v>
       </c>
       <c r="E5" s="4">
-        <v>74.10388215436517</v>
+        <v>73.24842719042508</v>
       </c>
       <c r="F5" s="4">
-        <v>82.50550873828932</v>
+        <v>82.42418125851596</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3518633247176944</v>
+      </c>
+      <c r="O5" s="5">
+        <v>123</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2994930234379792</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2108086618467195</v>
+      </c>
+      <c r="R5" s="5">
+        <v>123</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1542,6 +1651,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1549,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1560,9 +1670,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1596,8 +1712,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1619,132 +1743,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>1.465426548921775</v>
+        <v>0.7628882336263217</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4123850299119009</v>
+        <v>0.3749493875306493</v>
       </c>
       <c r="D3" s="4">
-        <v>3.663506781874138</v>
+        <v>0.379671829722608</v>
       </c>
       <c r="E3" s="4">
-        <v>67.28257770173947</v>
+        <v>65.53240457859792</v>
       </c>
       <c r="F3" s="4">
-        <v>73.54492357566635</v>
+        <v>73.98357647121941</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K3" s="5">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08583985440549879</v>
+      </c>
+      <c r="O3" s="5">
+        <v>130</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7500533766997246</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.371007357738055</v>
+      </c>
+      <c r="R3" s="5">
+        <v>130</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5116434190359392</v>
+        <v>0.7030760021491973</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3675105541466716</v>
+        <v>0.5813798161105769</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2698421571945678</v>
+        <v>0.4649739893544306</v>
       </c>
       <c r="E4" s="4">
-        <v>77.13774231497089</v>
+        <v>70.8802618791876</v>
       </c>
       <c r="F4" s="4">
-        <v>85.37669677549563</v>
+        <v>81.56187448486938</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5548379821807725</v>
+      </c>
+      <c r="O4" s="5">
+        <v>118</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5356592011746506</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3905854871199489</v>
+      </c>
+      <c r="R4" s="5">
+        <v>117</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5587855115476472</v>
+        <v>1.058409870759903</v>
       </c>
       <c r="C5" s="4">
-        <v>0.389514027531853</v>
+        <v>0.870070043391025</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2752178589280733</v>
+        <v>0.8135137824955775</v>
       </c>
       <c r="E5" s="4">
-        <v>75.59587744872402</v>
+        <v>71.22397831312949</v>
       </c>
       <c r="F5" s="4">
-        <v>84.2582126457071</v>
+        <v>79.89058216009781</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.780143660416436</v>
+      </c>
+      <c r="O5" s="5">
+        <v>112</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7176784047361636</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.580295740323382</v>
+      </c>
+      <c r="R5" s="5">
+        <v>111</v>
+      </c>
+      <c r="S5" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1755,6 +1951,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1762,7 +1959,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1773,9 +1970,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1809,8 +2012,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1832,132 +2043,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9985915527439071</v>
+        <v>0.4778777165825168</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4747847829037528</v>
+        <v>0.3468308513950089</v>
       </c>
       <c r="D3" s="4">
-        <v>1.19667078956793</v>
+        <v>0.2266284745811665</v>
       </c>
       <c r="E3" s="4">
-        <v>69.20404089779638</v>
+        <v>70.80553179355603</v>
       </c>
       <c r="F3" s="4">
-        <v>76.53083095553933</v>
+        <v>77.9445136572491</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="K3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M3" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.297179501800264</v>
+      </c>
+      <c r="O3" s="5">
+        <v>141</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.368507840212233</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2594466009139301</v>
+      </c>
+      <c r="R3" s="5">
+        <v>141</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.59638422956266</v>
+        <v>0.3906891263872809</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4422385041861113</v>
+        <v>0.2731464151325319</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3122265157628953</v>
+        <v>0.2743906321625988</v>
       </c>
       <c r="E4" s="4">
-        <v>73.16863587540254</v>
+        <v>74.10388215436517</v>
       </c>
       <c r="F4" s="4">
-        <v>81.53765285697366</v>
+        <v>82.50550873828932</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1095447093052</v>
+      </c>
+      <c r="O4" s="5">
+        <v>122</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3912853342218401</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2738017510167993</v>
+      </c>
+      <c r="R4" s="5">
+        <v>121</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4185572022138668</v>
+        <v>0.3922117648842332</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3021214062160126</v>
+        <v>0.2928242381625077</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2578364783953056</v>
+        <v>0.2012060830280189</v>
       </c>
       <c r="E5" s="4">
-        <v>73.15047823640697</v>
+        <v>74.35169556544409</v>
       </c>
       <c r="F5" s="4">
-        <v>82.37523338547653</v>
+        <v>81.9856688701629</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>9</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2335419430661255</v>
+      </c>
+      <c r="O5" s="5">
+        <v>122</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3381272982813137</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2360005332749098</v>
+      </c>
+      <c r="R5" s="5">
+        <v>122</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1968,6 +2251,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1975,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1986,9 +2270,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2022,8 +2312,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2045,132 +2343,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>1.890218336711228</v>
+        <v>1.465426548921775</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3414775351671062</v>
+        <v>0.4123850299119009</v>
       </c>
       <c r="D3" s="4">
-        <v>2.659853939062983</v>
+        <v>3.663506781874138</v>
       </c>
       <c r="E3" s="4">
-        <v>58.82683612367097</v>
+        <v>67.28257770173947</v>
       </c>
       <c r="F3" s="4">
-        <v>62.45421907862081</v>
+        <v>73.54492357566635</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="I3" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K3" s="5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L3" s="5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.142229700186482</v>
+      </c>
+      <c r="O3" s="5">
+        <v>94</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.475179421147962</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3767540741166496</v>
+      </c>
+      <c r="R3" s="5">
+        <v>94</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.522137976637176</v>
+        <v>0.5587855115476472</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3367774505152025</v>
+        <v>0.389514027531853</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2046158599074108</v>
+        <v>0.2752178589280733</v>
       </c>
       <c r="E4" s="4">
-        <v>70.1723696997595</v>
+        <v>75.59587744872402</v>
       </c>
       <c r="F4" s="4">
-        <v>79.73154362416152</v>
+        <v>84.2582126457071</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2989839209018834</v>
+      </c>
+      <c r="O4" s="5">
+        <v>126</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4792960007830551</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3196896904148596</v>
+      </c>
+      <c r="R4" s="5">
+        <v>125</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4151124238970509</v>
+        <v>0.5116434190359392</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2525059382352848</v>
+        <v>0.3675105541466716</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2123715527530412</v>
+        <v>0.2698421571945678</v>
       </c>
       <c r="E5" s="4">
-        <v>70.53347654851405</v>
+        <v>77.13774231497089</v>
       </c>
       <c r="F5" s="4">
-        <v>80.55608820709598</v>
+        <v>85.37669677549563</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2917573546546011</v>
+      </c>
+      <c r="O5" s="5">
+        <v>126</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4308677278179446</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2881434015402383</v>
+      </c>
+      <c r="R5" s="5">
+        <v>126</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2181,6 +2551,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2188,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2199,9 +2570,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2235,8 +2612,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2258,132 +2643,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>1.502877758373168</v>
+        <v>0.9985915527439071</v>
       </c>
       <c r="C3" s="4">
-        <v>1.166302128411253</v>
+        <v>0.4747847829037528</v>
       </c>
       <c r="D3" s="4">
-        <v>1.067619126137881</v>
+        <v>1.19667078956793</v>
       </c>
       <c r="E3" s="4">
-        <v>62.47688296875623</v>
+        <v>69.20404089779638</v>
       </c>
       <c r="F3" s="4">
-        <v>73.82831652131917</v>
+        <v>76.53083095553933</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="K3" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L3" s="5">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>5</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1182012928468722</v>
+      </c>
+      <c r="O3" s="5">
+        <v>127</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.028169766148392</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5283688857510873</v>
+      </c>
+      <c r="R3" s="5">
+        <v>122</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3583544442014966</v>
+        <v>0.4185572022138668</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1978839976680803</v>
+        <v>0.3021214062160126</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1096559732031812</v>
+        <v>0.2578364783953056</v>
       </c>
       <c r="E4" s="4">
-        <v>65.52478134110797</v>
+        <v>73.15047823640697</v>
       </c>
       <c r="F4" s="4">
-        <v>79.06780373753207</v>
+        <v>82.37523338547653</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3102261423190073</v>
+      </c>
+      <c r="O4" s="5">
+        <v>120</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3276091873039173</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2025772345933842</v>
+      </c>
+      <c r="R4" s="5">
+        <v>119</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2876166849720065</v>
+        <v>0.59638422956266</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1583386079172682</v>
+        <v>0.4422385041861113</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1142460040801981</v>
+        <v>0.3122265157628953</v>
       </c>
       <c r="E5" s="4">
-        <v>66.59326888650207</v>
+        <v>73.16863587540254</v>
       </c>
       <c r="F5" s="4">
-        <v>79.34239962321753</v>
+        <v>81.53765285697366</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4555411943082704</v>
+      </c>
+      <c r="O5" s="5">
+        <v>120</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3497385831207974</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1872697142784569</v>
+      </c>
+      <c r="R5" s="5">
+        <v>120</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2394,6 +2851,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2401,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2412,9 +2870,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2448,8 +2912,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2471,132 +2943,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>1.227410594454836</v>
+        <v>1.890218336711228</v>
       </c>
       <c r="C3" s="4">
-        <v>1.072630272622182</v>
+        <v>0.3414775351671062</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9292114840462651</v>
+        <v>2.659853939062983</v>
       </c>
       <c r="E3" s="4">
-        <v>70.10330057949123</v>
+        <v>58.82683612367097</v>
       </c>
       <c r="F3" s="4">
-        <v>77.68050376998848</v>
+        <v>62.45421907862081</v>
       </c>
       <c r="G3" s="5">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="H3" s="5">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J3" s="5">
+        <v>73</v>
+      </c>
+      <c r="K3" s="5">
         <v>26</v>
       </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M3" s="5">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2661702604934764</v>
+      </c>
+      <c r="O3" s="5">
+        <v>86</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.943610561484853</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5739302001402617</v>
+      </c>
+      <c r="R3" s="5">
+        <v>75</v>
+      </c>
+      <c r="S3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4151124238970509</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2525059382352848</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2123715527530412</v>
+      </c>
+      <c r="E4" s="4">
+        <v>70.53347654851405</v>
+      </c>
+      <c r="F4" s="4">
+        <v>80.55608820709598</v>
+      </c>
+      <c r="G4" s="5">
+        <v>133</v>
+      </c>
+      <c r="H4" s="5">
+        <v>115</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>18</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7048476437743156</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6531865691163062</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5096632472081185</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.31916099773252</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.05567984091461</v>
-      </c>
-      <c r="G4" s="5">
-        <v>108</v>
-      </c>
-      <c r="H4" s="5">
-        <v>97</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>11</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="N4" s="4">
+        <v>-0.1858256329306946</v>
+      </c>
+      <c r="O4" s="5">
+        <v>116</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3884776593345143</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2234139046255266</v>
+      </c>
+      <c r="R4" s="5">
+        <v>115</v>
+      </c>
+      <c r="S4" s="5">
         <v>1</v>
       </c>
-      <c r="L4" s="5">
-        <v>8</v>
-      </c>
-      <c r="M4" s="5">
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.522137976637176</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3367774505152025</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2046158599074108</v>
+      </c>
+      <c r="E5" s="4">
+        <v>70.1723696997595</v>
+      </c>
+      <c r="F5" s="4">
+        <v>79.73154362416152</v>
+      </c>
+      <c r="G5" s="5">
+        <v>133</v>
+      </c>
+      <c r="H5" s="5">
+        <v>115</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>18</v>
+      </c>
+      <c r="K5" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3675305656429393</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2717932819567161</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1929773612728055</v>
-      </c>
-      <c r="E5" s="4">
-        <v>73.38451268357794</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.91726776641937</v>
-      </c>
-      <c r="G5" s="5">
-        <v>107</v>
-      </c>
-      <c r="H5" s="5">
-        <v>96</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>11</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
       <c r="L5" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3270511166028384</v>
+      </c>
+      <c r="O5" s="5">
+        <v>115</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3958798208294694</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.207771891628649</v>
+      </c>
+      <c r="R5" s="5">
+        <v>115</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2607,6 +3151,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2614,7 +3159,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2625,9 +3170,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2661,8 +3212,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2684,107 +3243,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9009124693022745</v>
+        <v>1.502877758373168</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6691563647812495</v>
+        <v>1.166302128411253</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5852326612490608</v>
+        <v>1.067619126137881</v>
       </c>
       <c r="E3" s="4">
-        <v>63.52967534319107</v>
+        <v>62.47688296875623</v>
       </c>
       <c r="F3" s="4">
-        <v>74.46295328805475</v>
+        <v>73.82831652131917</v>
       </c>
       <c r="G3" s="5">
         <v>167</v>
       </c>
       <c r="H3" s="5">
+        <v>112</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>55</v>
+      </c>
+      <c r="K3" s="5">
+        <v>11</v>
+      </c>
+      <c r="L3" s="5">
+        <v>42</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.182860968285333</v>
+      </c>
+      <c r="O3" s="5">
         <v>114</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>53</v>
-      </c>
-      <c r="K3" s="5">
-        <v>4</v>
-      </c>
-      <c r="L3" s="5">
-        <v>49</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>0.517835511090211</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1691236676239521</v>
+      </c>
+      <c r="R3" s="5">
+        <v>114</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3413589402839691</v>
+        <v>0.2876166849720065</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1846243452934488</v>
+        <v>0.1583386079172682</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1307963707934951</v>
+        <v>0.1142460040801981</v>
       </c>
       <c r="E4" s="4">
-        <v>66.38304946038568</v>
+        <v>66.59326888650207</v>
       </c>
       <c r="F4" s="4">
-        <v>79.81648752754278</v>
+        <v>79.34239962321753</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1043825601986545</v>
+      </c>
+      <c r="O4" s="5">
+        <v>105</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2681075967558987</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1362928987022743</v>
+      </c>
+      <c r="R4" s="5">
+        <v>105</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4515905575474364</v>
+        <v>0.3583544442014966</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1895072010488704</v>
+        <v>0.1978839976680803</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1503523297016494</v>
+        <v>0.1096559732031812</v>
       </c>
       <c r="E5" s="4">
-        <v>66.65618126950002</v>
+        <v>65.52478134110797</v>
       </c>
       <c r="F5" s="4">
-        <v>79.27679938100248</v>
+        <v>79.06780373753207</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
@@ -2799,17 +3412,35 @@
         <v>32</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.178671041605504</v>
+      </c>
+      <c r="O5" s="5">
+        <v>101</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3076583748476041</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1318343910258057</v>
+      </c>
+      <c r="R5" s="5">
+        <v>101</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2820,12 +3451,1420 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.227410594454836</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.072630272622182</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9292114840462651</v>
+      </c>
+      <c r="E3" s="4">
+        <v>70.10330057949123</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.68050376998848</v>
+      </c>
+      <c r="G3" s="5">
+        <v>135</v>
+      </c>
+      <c r="H3" s="5">
+        <v>109</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>22</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.084611364407861</v>
+      </c>
+      <c r="O3" s="5">
+        <v>110</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3481499880449833</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1893697638946354</v>
+      </c>
+      <c r="R3" s="5">
+        <v>110</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3675305656429393</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2717932819567161</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1929773612728055</v>
+      </c>
+      <c r="E4" s="4">
+        <v>73.38451268357794</v>
+      </c>
+      <c r="F4" s="4">
+        <v>82.91726776641937</v>
+      </c>
+      <c r="G4" s="5">
+        <v>107</v>
+      </c>
+      <c r="H4" s="5">
+        <v>96</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>11</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2940264420396352</v>
+      </c>
+      <c r="O4" s="5">
+        <v>97</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2578163265215124</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1577783071341969</v>
+      </c>
+      <c r="R4" s="5">
+        <v>96</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7048476437743156</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6531865691163062</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5096632472081185</v>
+      </c>
+      <c r="E5" s="4">
+        <v>73.31916099773252</v>
+      </c>
+      <c r="F5" s="4">
+        <v>82.05567984091461</v>
+      </c>
+      <c r="G5" s="5">
+        <v>108</v>
+      </c>
+      <c r="H5" s="5">
+        <v>97</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>11</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>8</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.6856247250323464</v>
+      </c>
+      <c r="O5" s="5">
+        <v>99</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2026680128019255</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1686751102433235</v>
+      </c>
+      <c r="R5" s="5">
+        <v>99</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9009124693022745</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6691563647812495</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5852326612490608</v>
+      </c>
+      <c r="E3" s="4">
+        <v>63.52967534319107</v>
+      </c>
+      <c r="F3" s="4">
+        <v>74.46295328805475</v>
+      </c>
+      <c r="G3" s="5">
+        <v>167</v>
+      </c>
+      <c r="H3" s="5">
+        <v>114</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>53</v>
+      </c>
+      <c r="K3" s="5">
+        <v>4</v>
+      </c>
+      <c r="L3" s="5">
+        <v>49</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6691563647812495</v>
+      </c>
+      <c r="O3" s="5">
+        <v>114</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4160687576282678</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1766017937077747</v>
+      </c>
+      <c r="R3" s="5">
+        <v>114</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4515905575474364</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1895072010488704</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1503523297016494</v>
+      </c>
+      <c r="E4" s="4">
+        <v>66.65618126950002</v>
+      </c>
+      <c r="F4" s="4">
+        <v>79.27679938100248</v>
+      </c>
+      <c r="G4" s="5">
+        <v>133</v>
+      </c>
+      <c r="H4" s="5">
+        <v>101</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>29</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1017829429126926</v>
+      </c>
+      <c r="O4" s="5">
+        <v>101</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.434661630028274</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1718258134506343</v>
+      </c>
+      <c r="R4" s="5">
+        <v>101</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3413589402839691</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1846243452934488</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1307963707934951</v>
+      </c>
+      <c r="E5" s="4">
+        <v>66.38304946038568</v>
+      </c>
+      <c r="F5" s="4">
+        <v>79.81648752754278</v>
+      </c>
+      <c r="G5" s="5">
+        <v>133</v>
+      </c>
+      <c r="H5" s="5">
+        <v>107</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>26</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5">
+        <v>23</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1267163308793582</v>
+      </c>
+      <c r="O5" s="5">
+        <v>107</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3232041010514921</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1599078234628848</v>
+      </c>
+      <c r="R5" s="5">
+        <v>107</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>70.52154195011337</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.401360544217687</v>
+      </c>
+      <c r="D3" s="3">
+        <v>26.07709750566893</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8.843537414965986</v>
+      </c>
+      <c r="F3" s="3">
+        <v>15.87301587301587</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.7559396222472047</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2641894019823265</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.640698930919372</v>
+      </c>
+      <c r="K3" s="4">
+        <v>66.82570533882486</v>
+      </c>
+      <c r="L3" s="4">
+        <v>74.33514942143948</v>
+      </c>
+      <c r="M3" s="5">
+        <v>441</v>
+      </c>
+      <c r="N3" s="5">
+        <v>5904281.548023224</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.13382276732357</v>
+      </c>
+      <c r="P3" s="5">
+        <v>178195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>82.99319727891157</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="D4" s="3">
+        <v>16.55328798185941</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.267573696145125</v>
+      </c>
+      <c r="F4" s="3">
+        <v>14.05895691609977</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.2267573696145125</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.7834016752675357</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3704943308870414</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3935997505680382</v>
+      </c>
+      <c r="K4" s="4">
+        <v>67.66015703333493</v>
+      </c>
+      <c r="L4" s="4">
+        <v>76.5716771421471</v>
+      </c>
+      <c r="M4" s="5">
+        <v>441</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4772790.107011795</v>
+      </c>
+      <c r="O4" s="4">
+        <v>46.90195759683764</v>
+      </c>
+      <c r="P4" s="5">
+        <v>101761</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>74.37641723356009</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.9070294784580499</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24.71655328798186</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5.215419501133787</v>
+      </c>
+      <c r="F5" s="3">
+        <v>14.73922902494331</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1.141386974759461</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.5243709123491131</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.640448331523389</v>
+      </c>
+      <c r="K5" s="4">
+        <v>68.74882379255556</v>
+      </c>
+      <c r="L5" s="4">
+        <v>77.36986815606276</v>
+      </c>
+      <c r="M5" s="5">
+        <v>441</v>
+      </c>
+      <c r="N5" s="5">
+        <v>14055194.36073303</v>
+      </c>
+      <c r="O5" s="4">
+        <v>128.6104621927349</v>
+      </c>
+      <c r="P5" s="5">
+        <v>109285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>79.81859410430839</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.9070294784580499</v>
+      </c>
+      <c r="D6" s="3">
+        <v>19.27437641723356</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.133786848072562</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17.68707482993197</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5305622365526469</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3976184009803528</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3869047559424133</v>
+      </c>
+      <c r="K6" s="4">
+        <v>64.86124608573591</v>
+      </c>
+      <c r="L6" s="4">
+        <v>74.12125178184772</v>
+      </c>
+      <c r="M6" s="5">
+        <v>441</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8386180.981636047</v>
+      </c>
+      <c r="O6" s="4">
+        <v>86.2855715203676</v>
+      </c>
+      <c r="P6" s="5">
+        <v>97191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>76.19047619047619</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="D7" s="3">
+        <v>23.35600907029479</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.6281179138322</v>
+      </c>
+      <c r="F7" s="3">
+        <v>17.23356009070295</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.494331065759637</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.8235684720882332</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.330340065742256</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.823269747675227</v>
+      </c>
+      <c r="K7" s="4">
+        <v>68.41570641862191</v>
+      </c>
+      <c r="L7" s="4">
+        <v>77.13877348105541</v>
+      </c>
+      <c r="M7" s="5">
+        <v>441</v>
+      </c>
+      <c r="N7" s="5">
+        <v>19673906.58664703</v>
+      </c>
+      <c r="O7" s="4">
+        <v>169.3559089485752</v>
+      </c>
+      <c r="P7" s="5">
+        <v>116169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>82.76643990929705</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.6802721088435374</v>
+      </c>
+      <c r="D8" s="3">
+        <v>16.55328798185941</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="F8" s="3">
+        <v>14.73922902494331</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5847999894685868</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.384320838029288</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.5610932895299359</v>
+      </c>
+      <c r="K8" s="4">
+        <v>70.34946858562003</v>
+      </c>
+      <c r="L8" s="4">
+        <v>78.80838241336899</v>
+      </c>
+      <c r="M8" s="5">
+        <v>441</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1038137.613534927</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.74351386544888</v>
+      </c>
+      <c r="P8" s="5">
+        <v>81464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>82.99319727891157</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.8140589569161</v>
+      </c>
+      <c r="D9" s="3">
+        <v>15.19274376417234</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.040816326530612</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12.6984126984127</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6633391480245471</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4342132089035781</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4529997163225444</v>
+      </c>
+      <c r="K9" s="4">
+        <v>68.92722168232389</v>
+      </c>
+      <c r="L9" s="4">
+        <v>78.19753255515536</v>
+      </c>
+      <c r="M9" s="5">
+        <v>441</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2843546.705245972</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.72310980882481</v>
+      </c>
+      <c r="P9" s="5">
+        <v>92554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>88.66213151927438</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>11.33786848072562</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9.750566893424036</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.2267573696145125</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3609055664663827</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2532960389623012</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2926838398615453</v>
+      </c>
+      <c r="K10" s="4">
+        <v>72.92972064109098</v>
+      </c>
+      <c r="L10" s="4">
+        <v>80.65462874187622</v>
+      </c>
+      <c r="M10" s="5">
+        <v>441</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6981918.64323616</v>
+      </c>
+      <c r="O10" s="4">
+        <v>91.07285970071821</v>
+      </c>
+      <c r="P10" s="5">
+        <v>76663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>80.04535147392289</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.453514739229025</v>
+      </c>
+      <c r="D11" s="3">
+        <v>19.50113378684807</v>
+      </c>
+      <c r="E11" s="3">
+        <v>7.709750566893423</v>
+      </c>
+      <c r="F11" s="3">
+        <v>11.56462585034014</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.2267573696145125</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.8358000251322414</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.319725877367049</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.597526353346871</v>
+      </c>
+      <c r="K11" s="4">
+        <v>72.93157172165924</v>
+      </c>
+      <c r="L11" s="4">
+        <v>80.59710237562541</v>
+      </c>
+      <c r="M11" s="5">
+        <v>441</v>
+      </c>
+      <c r="N11" s="5">
+        <v>6722461.027145386</v>
+      </c>
+      <c r="O11" s="4">
+        <v>38.62728562893104</v>
+      </c>
+      <c r="P11" s="5">
+        <v>174034</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>83.67346938775511</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.133786848072562</v>
+      </c>
+      <c r="D12" s="3">
+        <v>15.19274376417234</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.401360544217687</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10.43083900226757</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5944565835118317</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.3019073431086975</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.6149450555459232</v>
+      </c>
+      <c r="K12" s="4">
+        <v>71.69011368719823</v>
+      </c>
+      <c r="L12" s="4">
+        <v>79.95543482120709</v>
+      </c>
+      <c r="M12" s="5">
+        <v>441</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1718875.04529953</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.93221845006146</v>
+      </c>
+      <c r="P12" s="5">
+        <v>90791</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>70.52154195011337</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="D13" s="3">
+        <v>24.71655328798186</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6.802721088435375</v>
+      </c>
+      <c r="F13" s="3">
+        <v>15.19274376417234</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2.72108843537415</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.9747104203203282</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.299886614252612</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.178211804393811</v>
+      </c>
+      <c r="K13" s="4">
+        <v>66.05025683742871</v>
+      </c>
+      <c r="L13" s="4">
+        <v>73.49850603925385</v>
+      </c>
+      <c r="M13" s="5">
+        <v>441</v>
+      </c>
+      <c r="N13" s="5">
+        <v>11677021.2085247</v>
+      </c>
+      <c r="O13" s="4">
+        <v>75.73972880157163</v>
+      </c>
+      <c r="P13" s="5">
+        <v>154173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>73.90300230946882</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>26.09699769053118</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.311778290993072</v>
+      </c>
+      <c r="F14" s="3">
+        <v>20.78521939953811</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3765713731531896</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1465816436452366</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1799444426269757</v>
+      </c>
+      <c r="K14" s="4">
+        <v>64.67745989850899</v>
+      </c>
+      <c r="L14" s="4">
+        <v>77.13137622642047</v>
+      </c>
+      <c r="M14" s="5">
+        <v>433</v>
+      </c>
+      <c r="N14" s="5">
+        <v>25842723.15478325</v>
+      </c>
+      <c r="O14" s="4">
+        <v>238.4300991335054</v>
+      </c>
+      <c r="P14" s="5">
+        <v>108387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>87.14285714285714</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11.14285714285714</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2756421163042358</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1727089423848585</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2222757276873057</v>
+      </c>
+      <c r="K15" s="4">
+        <v>72.09873663751219</v>
+      </c>
+      <c r="L15" s="4">
+        <v>80.63151166506803</v>
+      </c>
+      <c r="M15" s="5">
+        <v>350</v>
+      </c>
+      <c r="N15" s="5">
+        <v>17141235.29887199</v>
+      </c>
+      <c r="O15" s="4">
+        <v>248.9179283341126</v>
+      </c>
+      <c r="P15" s="5">
+        <v>68863</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>74.364896073903</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>25.635103926097</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.309468822170901</v>
+      </c>
+      <c r="F16" s="3">
+        <v>23.3256351039261</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3932554844284749</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1695563625830095</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1799996594589194</v>
+      </c>
+      <c r="K16" s="4">
+        <v>65.36645143045666</v>
+      </c>
+      <c r="L16" s="4">
+        <v>77.58595925621674</v>
+      </c>
+      <c r="M16" s="5">
+        <v>433</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8895250.411272049</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.32540905360186</v>
+      </c>
+      <c r="P16" s="5">
+        <v>91397</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2939,16 +4978,16 @@
         <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2983,16 +5022,16 @@
         <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3027,16 +5066,16 @@
         <v>9</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3071,16 +5110,16 @@
         <v>4</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3115,16 +5154,16 @@
         <v>3</v>
       </c>
       <c r="K7" s="5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L7" s="5">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3159,16 +5198,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3203,16 +5242,16 @@
         <v>3</v>
       </c>
       <c r="K9" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" s="5">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3247,16 +5286,16 @@
         <v>3</v>
       </c>
       <c r="K10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3291,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="L11" s="5">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3338,13 +5377,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="M12" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3379,16 +5418,16 @@
         <v>6</v>
       </c>
       <c r="K13" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="M13" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N13" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3423,16 +5462,16 @@
         <v>17</v>
       </c>
       <c r="K14" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="M14" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3467,16 +5506,16 @@
         <v>2</v>
       </c>
       <c r="K15" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3511,16 +5550,16 @@
         <v>2</v>
       </c>
       <c r="K16" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="M16" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3536,9 +5575,720 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>311</v>
+      </c>
+      <c r="C3" s="5">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5">
+        <v>115</v>
+      </c>
+      <c r="E3" s="5">
+        <v>39</v>
+      </c>
+      <c r="F3" s="5">
+        <v>70</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>39</v>
+      </c>
+      <c r="I3" s="5">
+        <v>32</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
+        <v>68</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>366</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <v>62</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>60</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>328</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5">
+        <v>23</v>
+      </c>
+      <c r="F5" s="5">
+        <v>65</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>23</v>
+      </c>
+      <c r="I5" s="5">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5">
+        <v>9</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>61</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>352</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>85</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>78</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>69</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>336</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>103</v>
+      </c>
+      <c r="E7" s="5">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5">
+        <v>76</v>
+      </c>
+      <c r="G7" s="5">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5">
+        <v>12</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>5</v>
+      </c>
+      <c r="L7" s="5">
+        <v>59</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>365</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>73</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5">
+        <v>6</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>55</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>366</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>67</v>
+      </c>
+      <c r="E9" s="5">
+        <v>9</v>
+      </c>
+      <c r="F9" s="5">
+        <v>56</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>9</v>
+      </c>
+      <c r="I9" s="5">
+        <v>7</v>
+      </c>
+      <c r="J9" s="5">
+        <v>3</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>41</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>391</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>50</v>
+      </c>
+      <c r="E10" s="5">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5">
+        <v>43</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>3</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5">
+        <v>3</v>
+      </c>
+      <c r="L10" s="5">
+        <v>34</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>353</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>86</v>
+      </c>
+      <c r="E11" s="5">
+        <v>34</v>
+      </c>
+      <c r="F11" s="5">
+        <v>51</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
+        <v>34</v>
+      </c>
+      <c r="I11" s="5">
+        <v>34</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>12</v>
+      </c>
+      <c r="L11" s="5">
+        <v>39</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>369</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>67</v>
+      </c>
+      <c r="E12" s="5">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5">
+        <v>46</v>
+      </c>
+      <c r="G12" s="5">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5">
+        <v>15</v>
+      </c>
+      <c r="I12" s="5">
+        <v>6</v>
+      </c>
+      <c r="J12" s="5">
+        <v>11</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>40</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>311</v>
+      </c>
+      <c r="C13" s="5">
+        <v>21</v>
+      </c>
+      <c r="D13" s="5">
+        <v>109</v>
+      </c>
+      <c r="E13" s="5">
+        <v>30</v>
+      </c>
+      <c r="F13" s="5">
+        <v>67</v>
+      </c>
+      <c r="G13" s="5">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5">
+        <v>25</v>
+      </c>
+      <c r="J13" s="5">
+        <v>6</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>59</v>
+      </c>
+      <c r="M13" s="5">
+        <v>3</v>
+      </c>
+      <c r="N13" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>320</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5">
+        <v>23</v>
+      </c>
+      <c r="F14" s="5">
+        <v>90</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>23</v>
+      </c>
+      <c r="I14" s="5">
+        <v>7</v>
+      </c>
+      <c r="J14" s="5">
+        <v>17</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>79</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>305</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>45</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
+      <c r="I15" s="5">
+        <v>3</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5">
+        <v>2</v>
+      </c>
+      <c r="L15" s="5">
+        <v>30</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>322</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>111</v>
+      </c>
+      <c r="E16" s="5">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5">
+        <v>101</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>10</v>
+      </c>
+      <c r="I16" s="5">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
+        <v>2</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>93</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3549,9 +6299,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3585,8 +6341,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3608,10 +6372,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>1.296777739483036</v>
@@ -3649,91 +6431,145 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1642927784796811</v>
+      </c>
+      <c r="O3" s="5">
+        <v>83</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.27594369601983</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3538123706579795</v>
+      </c>
+      <c r="R3" s="5">
+        <v>78</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4765150458266286</v>
+        <v>0.5022125422779766</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2328341906656337</v>
+        <v>0.3007598757987192</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2270665900406779</v>
+        <v>0.2845841987397003</v>
       </c>
       <c r="E4" s="4">
-        <v>71.02987059485423</v>
+        <v>71.98020561608104</v>
       </c>
       <c r="F4" s="4">
-        <v>80.3190863063717</v>
+        <v>81.0837496425624</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2287051283657278</v>
+      </c>
+      <c r="O4" s="5">
+        <v>116</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4381863668313623</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2479642103305954</v>
+      </c>
+      <c r="R4" s="5">
+        <v>115</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5022125422779766</v>
+        <v>0.4765150458266286</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3007598757987192</v>
+        <v>0.2328341906656337</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2845841987397003</v>
+        <v>0.2270665900406779</v>
       </c>
       <c r="E5" s="4">
-        <v>71.98020561608104</v>
+        <v>71.02987059485423</v>
       </c>
       <c r="F5" s="4">
-        <v>81.0837496425624</v>
+        <v>80.3190863063717</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1506834689535106</v>
+      </c>
+      <c r="O5" s="5">
+        <v>112</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.459296438902963</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2274773970977599</v>
+      </c>
+      <c r="R5" s="5">
+        <v>112</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3744,14 +6580,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3762,9 +6599,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3798,8 +6641,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3821,10 +6672,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>1.014521022627831</v>
@@ -3862,25 +6731,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4109474591893756</v>
+      </c>
+      <c r="O3" s="5">
+        <v>125</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8293862554076529</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.349064333470391</v>
+      </c>
+      <c r="R3" s="5">
+        <v>125</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9105254385507608</v>
+        <v>0.9633453838175856</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4534985589050829</v>
+        <v>0.585482218527975</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3932077767321149</v>
+        <v>0.4808518650105703</v>
       </c>
       <c r="E4" s="4">
-        <v>71.60196409390819</v>
+        <v>69.72226484578755</v>
       </c>
       <c r="F4" s="4">
-        <v>80.642377756473</v>
+        <v>79.112798775461</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
@@ -3895,33 +6782,51 @@
         <v>16</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.5345381396759932</v>
+      </c>
+      <c r="O4" s="5">
+        <v>118</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7289035621959985</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.383317998249511</v>
+      </c>
+      <c r="R4" s="5">
+        <v>117</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9633453838175856</v>
+        <v>0.9105254385507608</v>
       </c>
       <c r="C5" s="4">
-        <v>0.585482218527975</v>
+        <v>0.4534985589050829</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4808518650105703</v>
+        <v>0.3932077767321149</v>
       </c>
       <c r="E5" s="4">
-        <v>69.72226484578755</v>
+        <v>71.60196409390819</v>
       </c>
       <c r="F5" s="4">
-        <v>79.112798775461</v>
+        <v>80.642377756473</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
@@ -3936,17 +6841,35 @@
         <v>16</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3186817634732127</v>
+      </c>
+      <c r="O5" s="5">
+        <v>118</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.817533118186865</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3910728253686231</v>
+      </c>
+      <c r="R5" s="5">
+        <v>118</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3957,14 +6880,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3975,9 +6899,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4011,8 +6941,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4034,10 +6972,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>2.10490321284595</v>
@@ -4075,91 +7031,145 @@
       <c r="M3" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.02877703237198</v>
+      </c>
+      <c r="O3" s="5">
+        <v>111</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.51877669553776</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.343472383471488</v>
+      </c>
+      <c r="R3" s="5">
+        <v>91</v>
+      </c>
+      <c r="S3" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.404724638096886</v>
+        <v>0.4333969059945339</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3279963693814262</v>
+        <v>0.3418999843375052</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2321970420814551</v>
+        <v>0.2667786928888931</v>
       </c>
       <c r="E4" s="4">
-        <v>70.81300189248643</v>
+        <v>70.48002659710464</v>
       </c>
       <c r="F4" s="4">
-        <v>80.37947217035737</v>
+        <v>79.94550133723456</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
         <v>17</v>
       </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>14</v>
-      </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3434277635790269</v>
+      </c>
+      <c r="O4" s="5">
+        <v>114</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3276618998575161</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2224346942637024</v>
+      </c>
+      <c r="R4" s="5">
+        <v>113</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4333969059945339</v>
+        <v>0.404724638096886</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3418999843375052</v>
+        <v>0.3279963693814262</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2667786928888931</v>
+        <v>0.2321970420814551</v>
       </c>
       <c r="E5" s="4">
-        <v>70.48002659710464</v>
+        <v>70.81300189248643</v>
       </c>
       <c r="F5" s="4">
-        <v>79.94550133723456</v>
+        <v>80.37947217035737</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.316109184758543</v>
+      </c>
+      <c r="O5" s="5">
+        <v>116</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2889274881229884</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2059740757766914</v>
+      </c>
+      <c r="R5" s="5">
+        <v>116</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4170,14 +7180,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4188,9 +7199,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4224,8 +7241,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4247,10 +7272,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.5574432514665979</v>
@@ -4288,25 +7331,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1070374288134773</v>
+      </c>
+      <c r="O3" s="5">
+        <v>124</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5371763293278971</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3798251200343382</v>
+      </c>
+      <c r="R3" s="5">
+        <v>124</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6227445009904777</v>
+        <v>0.6491904388761436</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4440856750132416</v>
+        <v>0.5246404794086056</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3546709459151789</v>
+        <v>0.398405306301819</v>
       </c>
       <c r="E4" s="4">
-        <v>65.93550202035686</v>
+        <v>66.01043424888742</v>
       </c>
       <c r="F4" s="4">
-        <v>75.12741585507399</v>
+        <v>76.3908092378614</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
@@ -4329,25 +7390,43 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4348392061362967</v>
+      </c>
+      <c r="O4" s="5">
+        <v>112</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5187962554989858</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4209342099439887</v>
+      </c>
+      <c r="R4" s="5">
+        <v>111</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6491904388761436</v>
+        <v>0.6227445009904777</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5246404794086056</v>
+        <v>0.4440856750132416</v>
       </c>
       <c r="D5" s="4">
-        <v>0.398405306301819</v>
+        <v>0.3546709459151789</v>
       </c>
       <c r="E5" s="4">
-        <v>66.01043424888742</v>
+        <v>65.93550202035686</v>
       </c>
       <c r="F5" s="4">
-        <v>76.3908092378614</v>
+        <v>75.12741585507399</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
@@ -4370,9 +7449,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.298715712976076</v>
+      </c>
+      <c r="O5" s="5">
+        <v>112</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5547545352325215</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4083456433749695</v>
+      </c>
+      <c r="R5" s="5">
+        <v>111</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4383,14 +7480,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4401,9 +7499,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4437,8 +7541,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4460,10 +7572,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>1.488366384902373</v>
@@ -4501,91 +7631,145 @@
       <c r="M3" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4224707645182293</v>
+      </c>
+      <c r="O3" s="5">
+        <v>108</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.708066758882752</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7490867050740722</v>
+      </c>
+      <c r="R3" s="5">
+        <v>98</v>
+      </c>
+      <c r="S3" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4526836907076427</v>
+        <v>0.3070060621450673</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3598777853551956</v>
+        <v>0.1712865792028572</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1944155474186821</v>
+        <v>0.1382986469094448</v>
       </c>
       <c r="E4" s="4">
-        <v>71.31962559459821</v>
+        <v>71.04061173341495</v>
       </c>
       <c r="F4" s="4">
-        <v>80.59250475181189</v>
+        <v>80.42438310541328</v>
       </c>
       <c r="G4" s="5">
         <v>133</v>
       </c>
       <c r="H4" s="5">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.112665660820044</v>
+      </c>
+      <c r="O4" s="5">
+        <v>115</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2954531537537741</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1554569600021981</v>
+      </c>
+      <c r="R4" s="5">
+        <v>114</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3070060621450673</v>
+        <v>0.4526836907076427</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1712865792028572</v>
+        <v>0.3598777853551956</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1382986469094448</v>
+        <v>0.1944155474186821</v>
       </c>
       <c r="E5" s="4">
-        <v>71.04061173341495</v>
+        <v>71.31962559459821</v>
       </c>
       <c r="F5" s="4">
-        <v>80.42438310541328</v>
+        <v>80.59250475181189</v>
       </c>
       <c r="G5" s="5">
         <v>133</v>
       </c>
       <c r="H5" s="5">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3574979797836144</v>
+      </c>
+      <c r="O5" s="5">
+        <v>117</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2865420907228443</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1655335919389781</v>
+      </c>
+      <c r="R5" s="5">
+        <v>117</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4596,432 +7780,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.016225177535246</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7059060113183256</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.047774118887867</v>
-      </c>
-      <c r="E3" s="4">
-        <v>66.41411055440146</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.1051320178434</v>
-      </c>
-      <c r="G3" s="5">
-        <v>167</v>
-      </c>
-      <c r="H3" s="5">
-        <v>114</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>50</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>42</v>
-      </c>
-      <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4467732705209551</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3658073156074957</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2637966749598041</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.24842719042508</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.42418125851596</v>
-      </c>
-      <c r="G4" s="5">
-        <v>133</v>
-      </c>
-      <c r="H4" s="5">
-        <v>123</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7240268212617482</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6310667018862659</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5277516273496105</v>
-      </c>
-      <c r="E5" s="4">
-        <v>72.32622372257148</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.16051874653105</v>
-      </c>
-      <c r="G5" s="5">
-        <v>133</v>
-      </c>
-      <c r="H5" s="5">
-        <v>118</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>15</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>14</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7628882336263217</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3749493875306493</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.379671829722608</v>
-      </c>
-      <c r="E3" s="4">
-        <v>65.53240457859792</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.98357647121941</v>
-      </c>
-      <c r="G3" s="5">
-        <v>167</v>
-      </c>
-      <c r="H3" s="5">
-        <v>130</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5">
-        <v>30</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.058409870759903</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.870070043391025</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.8135137824955775</v>
-      </c>
-      <c r="E4" s="4">
-        <v>71.22397831312949</v>
-      </c>
-      <c r="F4" s="4">
-        <v>79.89058216009781</v>
-      </c>
-      <c r="G4" s="5">
-        <v>133</v>
-      </c>
-      <c r="H4" s="5">
-        <v>109</v>
-      </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
-      <c r="J4" s="5">
-        <v>17</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>12</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7030760021491973</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5813798161105769</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4649739893544306</v>
-      </c>
-      <c r="E5" s="4">
-        <v>70.8802618791876</v>
-      </c>
-      <c r="F5" s="4">
-        <v>81.56187448486938</v>
-      </c>
-      <c r="G5" s="5">
-        <v>133</v>
-      </c>
-      <c r="H5" s="5">
-        <v>117</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>16</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>14</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SainiElectronic2022.xlsx
+++ b/public/downloads/SainiElectronic2022.xlsx
@@ -1503,22 +1503,22 @@
         <v>7</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1677176189456047</v>
+        <v>-0.2747297661165167</v>
       </c>
       <c r="O3" s="5">
         <v>121</v>
       </c>
       <c r="P3" s="4">
-        <v>1.059937190443817</v>
+        <v>0.9763344345047246</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7872032508665375</v>
+        <v>0.5445737515232467</v>
       </c>
       <c r="R3" s="5">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="S3" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1562,16 +1562,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6559463275487086</v>
+        <v>-0.635393400505059</v>
       </c>
       <c r="O4" s="5">
         <v>119</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3012795312585546</v>
+        <v>0.3003284241114182</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1868434626791098</v>
+        <v>0.1859456294288937</v>
       </c>
       <c r="R4" s="5">
         <v>118</v>
@@ -1621,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3518633247176944</v>
+        <v>-0.316027627730417</v>
       </c>
       <c r="O5" s="5">
         <v>123</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2994930234379792</v>
+        <v>0.2980779442299481</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2108086618467195</v>
+        <v>0.2092785355486045</v>
       </c>
       <c r="R5" s="5">
         <v>123</v>
@@ -1803,16 +1803,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08583985440549879</v>
+        <v>-0.06558150006836172</v>
       </c>
       <c r="O3" s="5">
         <v>130</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7500533766997246</v>
+        <v>0.7518131244596744</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.371007357738055</v>
+        <v>0.370307120380409</v>
       </c>
       <c r="R3" s="5">
         <v>130</v>
@@ -1862,16 +1862,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5548379821807725</v>
+        <v>-0.4947812046887137</v>
       </c>
       <c r="O4" s="5">
         <v>118</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5356592011746506</v>
+        <v>0.5311513773353795</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3905854871199489</v>
+        <v>0.3875551623956666</v>
       </c>
       <c r="R4" s="5">
         <v>117</v>
@@ -1921,16 +1921,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.780143660416436</v>
+        <v>-0.9373789154077201</v>
       </c>
       <c r="O5" s="5">
         <v>112</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7176784047361636</v>
+        <v>0.690911707375029</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.580295740323382</v>
+        <v>0.5596806591355223</v>
       </c>
       <c r="R5" s="5">
         <v>111</v>
@@ -2103,16 +2103,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.297179501800264</v>
+        <v>-0.3077822215686581</v>
       </c>
       <c r="O3" s="5">
         <v>141</v>
       </c>
       <c r="P3" s="4">
-        <v>0.368507840212233</v>
+        <v>0.3671745640736925</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2594466009139301</v>
+        <v>0.259371404319828</v>
       </c>
       <c r="R3" s="5">
         <v>141</v>
@@ -2162,16 +2162,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1095447093052</v>
+        <v>-0.05530924026020401</v>
       </c>
       <c r="O4" s="5">
         <v>122</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3912853342218401</v>
+        <v>0.3882926503660412</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2738017510167993</v>
+        <v>0.2705122720678634</v>
       </c>
       <c r="R4" s="5">
         <v>121</v>
@@ -2221,16 +2221,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2335419430661255</v>
+        <v>-0.2121367069916467</v>
       </c>
       <c r="O5" s="5">
         <v>122</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3381272982813137</v>
+        <v>0.3371679455326699</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2360005332749098</v>
+        <v>0.2351301342626546</v>
       </c>
       <c r="R5" s="5">
         <v>122</v>
@@ -2403,22 +2403,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.142229700186482</v>
+        <v>-0.2042610111865244</v>
       </c>
       <c r="O3" s="5">
         <v>94</v>
       </c>
       <c r="P3" s="4">
-        <v>1.475179421147962</v>
+        <v>1.486670242772969</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3767540741166496</v>
+        <v>0.3382147591722564</v>
       </c>
       <c r="R3" s="5">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2462,16 +2462,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2989839209018834</v>
+        <v>-0.2554801812158232</v>
       </c>
       <c r="O4" s="5">
         <v>126</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4792960007830551</v>
+        <v>0.4797666035163026</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3196896904148596</v>
+        <v>0.3181022322181039</v>
       </c>
       <c r="R4" s="5">
         <v>125</v>
@@ -2521,16 +2521,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2917573546546011</v>
+        <v>-0.2833175394360339</v>
       </c>
       <c r="O5" s="5">
         <v>126</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4308677278179446</v>
+        <v>0.4307303173896417</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2881434015402383</v>
+        <v>0.2880653398597166</v>
       </c>
       <c r="R5" s="5">
         <v>126</v>
@@ -2703,16 +2703,16 @@
         <v>5</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1182012928468722</v>
+        <v>-0.2137692459081961</v>
       </c>
       <c r="O3" s="5">
         <v>127</v>
       </c>
       <c r="P3" s="4">
-        <v>1.028169766148392</v>
+        <v>0.9834508443482167</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5283688857510873</v>
+        <v>0.4251328212490387</v>
       </c>
       <c r="R3" s="5">
         <v>122</v>
@@ -2762,16 +2762,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3102261423190073</v>
+        <v>-0.246322557576903</v>
       </c>
       <c r="O4" s="5">
         <v>120</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3276091873039173</v>
+        <v>0.3186544523654107</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2025772345933842</v>
+        <v>0.1937501396777343</v>
       </c>
       <c r="R4" s="5">
         <v>119</v>
@@ -2821,16 +2821,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4555411943082704</v>
+        <v>-0.373787488728027</v>
       </c>
       <c r="O5" s="5">
         <v>120</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3497385831207974</v>
+        <v>0.3417301515200607</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1872697142784569</v>
+        <v>0.1805786162166349</v>
       </c>
       <c r="R5" s="5">
         <v>120</v>
@@ -3003,16 +3003,16 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2661702604934764</v>
+        <v>-0.2390719958142071</v>
       </c>
       <c r="O3" s="5">
         <v>86</v>
       </c>
       <c r="P3" s="4">
-        <v>1.943610561484853</v>
+        <v>1.892268990929897</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5739302001402617</v>
+        <v>0.2375554162158861</v>
       </c>
       <c r="R3" s="5">
         <v>75</v>
@@ -3062,16 +3062,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1858256329306946</v>
+        <v>-0.1354186598364251</v>
       </c>
       <c r="O4" s="5">
         <v>116</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3884776593345143</v>
+        <v>0.3830826776527982</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2234139046255266</v>
+        <v>0.2184104462078792</v>
       </c>
       <c r="R4" s="5">
         <v>115</v>
@@ -3121,16 +3121,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3270511166028384</v>
+        <v>-0.2924313720410225</v>
       </c>
       <c r="O5" s="5">
         <v>115</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3958798208294694</v>
+        <v>0.3941223987576374</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.207771891628649</v>
+        <v>0.2051373122836291</v>
       </c>
       <c r="R5" s="5">
         <v>115</v>
@@ -3303,16 +3303,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.182860968285333</v>
+        <v>-1.136537164194636</v>
       </c>
       <c r="O3" s="5">
         <v>114</v>
       </c>
       <c r="P3" s="4">
-        <v>0.517835511090211</v>
+        <v>0.5186912651752678</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1691236676239521</v>
+        <v>0.1655035879884009</v>
       </c>
       <c r="R3" s="5">
         <v>114</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1043825601986545</v>
+        <v>-0.1082881942702869</v>
       </c>
       <c r="O4" s="5">
         <v>105</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2681075967558987</v>
+        <v>0.2680782310861872</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1362928987022743</v>
+        <v>0.1362557021873063</v>
       </c>
       <c r="R4" s="5">
         <v>105</v>
@@ -3421,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.178671041605504</v>
+        <v>-0.1818932608559578</v>
       </c>
       <c r="O5" s="5">
         <v>101</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3076583748476041</v>
+        <v>0.3078342069567208</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1318343910258057</v>
+        <v>0.1317469007090531</v>
       </c>
       <c r="R5" s="5">
         <v>101</v>
@@ -3603,16 +3603,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.084611364407861</v>
+        <v>-1.049948555208371</v>
       </c>
       <c r="O3" s="5">
         <v>110</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3481499880449833</v>
+        <v>0.3468194016169671</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1893697638946354</v>
+        <v>0.1849007234348391</v>
       </c>
       <c r="R3" s="5">
         <v>110</v>
@@ -3662,16 +3662,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2940264420396352</v>
+        <v>-0.2576278468540636</v>
       </c>
       <c r="O4" s="5">
         <v>97</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2578163265215124</v>
+        <v>0.2542800871762673</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1577783071341969</v>
+        <v>0.1534577216641261</v>
       </c>
       <c r="R4" s="5">
         <v>96</v>
@@ -3721,16 +3721,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6856247250323464</v>
+        <v>-0.6459314526709825</v>
       </c>
       <c r="O5" s="5">
         <v>99</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2026680128019255</v>
+        <v>0.1987416577462702</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1686751102433235</v>
+        <v>0.1651851383933699</v>
       </c>
       <c r="R5" s="5">
         <v>99</v>
@@ -3903,16 +3903,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6691563647812495</v>
+        <v>-0.6541108598654981</v>
       </c>
       <c r="O3" s="5">
         <v>114</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4160687576282678</v>
+        <v>0.4174324582155001</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1766017937077747</v>
+        <v>0.1760919112925862</v>
       </c>
       <c r="R3" s="5">
         <v>114</v>
@@ -3962,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1017829429126926</v>
+        <v>-0.09179323725673072</v>
       </c>
       <c r="O4" s="5">
         <v>101</v>
       </c>
       <c r="P4" s="4">
-        <v>0.434661630028274</v>
+        <v>0.4343978234123878</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1718258134506343</v>
+        <v>0.1713761094071837</v>
       </c>
       <c r="R4" s="5">
         <v>101</v>
@@ -4021,16 +4021,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1267163308793582</v>
+        <v>-0.1097360395152975</v>
       </c>
       <c r="O5" s="5">
         <v>107</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3232041010514921</v>
+        <v>0.322261475162843</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1599078234628848</v>
+        <v>0.1593709255401364</v>
       </c>
       <c r="R5" s="5">
         <v>107</v>
@@ -4167,13 +4167,13 @@
         <v>1.360544217687075</v>
       </c>
       <c r="H3" s="4">
-        <v>0.7559396222472047</v>
+        <v>0.7586614509348255</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2641894019823265</v>
+        <v>0.2550633832656042</v>
       </c>
       <c r="J3" s="4">
-        <v>1.640698930919372</v>
+        <v>1.645739180090854</v>
       </c>
       <c r="K3" s="4">
         <v>66.82570533882486</v>
@@ -4217,13 +4217,13 @@
         <v>0.2267573696145125</v>
       </c>
       <c r="H4" s="4">
-        <v>0.7834016752675357</v>
+        <v>0.7843468752067283</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3704943308870414</v>
+        <v>0.3700757907049999</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3935997505680382</v>
+        <v>0.3907030899441354</v>
       </c>
       <c r="K4" s="4">
         <v>67.66015703333493</v>
@@ -4249,13 +4249,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>74.37641723356009</v>
+        <v>74.82993197278913</v>
       </c>
       <c r="C5" s="3">
         <v>0.9070294784580499</v>
       </c>
       <c r="D5" s="3">
-        <v>24.71655328798186</v>
+        <v>24.26303854875284</v>
       </c>
       <c r="E5" s="3">
         <v>5.215419501133787</v>
@@ -4264,16 +4264,16 @@
         <v>14.73922902494331</v>
       </c>
       <c r="G5" s="3">
-        <v>4.761904761904762</v>
+        <v>4.308390022675737</v>
       </c>
       <c r="H5" s="4">
-        <v>1.141386974759461</v>
+        <v>0.9684104811907479</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5243709123491131</v>
+        <v>0.2399752151960779</v>
       </c>
       <c r="J5" s="4">
-        <v>1.640448331523389</v>
+        <v>1.504976768013611</v>
       </c>
       <c r="K5" s="4">
         <v>68.74882379255556</v>
@@ -4317,13 +4317,13 @@
         <v>0.453514739229025</v>
       </c>
       <c r="H6" s="4">
-        <v>0.5305622365526469</v>
+        <v>0.5320380504742203</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3976184009803528</v>
+        <v>0.3951626585122961</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3869047559424133</v>
+        <v>0.3702055356286477</v>
       </c>
       <c r="K6" s="4">
         <v>64.86124608573591</v>
@@ -4367,13 +4367,13 @@
         <v>2.494331065759637</v>
       </c>
       <c r="H7" s="4">
-        <v>0.8235684720882332</v>
+        <v>0.7123116674979414</v>
       </c>
       <c r="I7" s="4">
-        <v>0.330340065742256</v>
+        <v>0.1794535923791509</v>
       </c>
       <c r="J7" s="4">
-        <v>0.823269747675227</v>
+        <v>0.7330096590653379</v>
       </c>
       <c r="K7" s="4">
         <v>68.41570641862191</v>
@@ -4399,13 +4399,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>82.76643990929705</v>
+        <v>80.72562358276643</v>
       </c>
       <c r="C8" s="3">
         <v>0.6802721088435374</v>
       </c>
       <c r="D8" s="3">
-        <v>16.55328798185941</v>
+        <v>18.59410430839002</v>
       </c>
       <c r="E8" s="3">
         <v>0.453514739229025</v>
@@ -4414,16 +4414,16 @@
         <v>14.73922902494331</v>
       </c>
       <c r="G8" s="3">
-        <v>1.360544217687075</v>
+        <v>3.401360544217687</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5847999894685868</v>
+        <v>0.5522194531165919</v>
       </c>
       <c r="I8" s="4">
-        <v>0.384320838029288</v>
+        <v>0.3001267326707907</v>
       </c>
       <c r="J8" s="4">
-        <v>0.5610932895299359</v>
+        <v>0.5531220209060032</v>
       </c>
       <c r="K8" s="4">
         <v>70.34946858562003</v>
@@ -4467,13 +4467,13 @@
         <v>0.453514739229025</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6633391480245471</v>
+        <v>0.654549554276015</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4342132089035781</v>
+        <v>0.4267147655690213</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4529997163225444</v>
+        <v>0.4526439836878441</v>
       </c>
       <c r="K9" s="4">
         <v>68.92722168232389</v>
@@ -4517,13 +4517,13 @@
         <v>0.2267573696145125</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3609055664663827</v>
+        <v>0.3591489633248318</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2532960389623012</v>
+        <v>0.251945628852242</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2926838398615453</v>
+        <v>0.2811824116236469</v>
       </c>
       <c r="K10" s="4">
         <v>72.92972064109098</v>
@@ -4549,13 +4549,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>80.04535147392289</v>
+        <v>79.59183673469387</v>
       </c>
       <c r="C11" s="3">
         <v>0.453514739229025</v>
       </c>
       <c r="D11" s="3">
-        <v>19.50113378684807</v>
+        <v>19.9546485260771</v>
       </c>
       <c r="E11" s="3">
         <v>7.709750566893423</v>
@@ -4564,16 +4564,16 @@
         <v>11.56462585034014</v>
       </c>
       <c r="G11" s="3">
-        <v>0.2267573696145125</v>
+        <v>0.6802721088435374</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8358000251322414</v>
+        <v>0.8402519112726807</v>
       </c>
       <c r="I11" s="4">
-        <v>0.319725877367049</v>
+        <v>0.3087061012567254</v>
       </c>
       <c r="J11" s="4">
-        <v>1.597526353346871</v>
+        <v>1.602719664251114</v>
       </c>
       <c r="K11" s="4">
         <v>72.93157172165924</v>
@@ -4617,13 +4617,13 @@
         <v>1.360544217687075</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5944565835118317</v>
+        <v>0.5724063316062791</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3019073431086975</v>
+        <v>0.2627524489850365</v>
       </c>
       <c r="J12" s="4">
-        <v>0.6149450555459232</v>
+        <v>0.6011673561564063</v>
       </c>
       <c r="K12" s="4">
         <v>71.69011368719823</v>
@@ -4667,13 +4667,13 @@
         <v>2.72108843537415</v>
       </c>
       <c r="H13" s="4">
-        <v>0.9747104203203282</v>
+        <v>0.9529697824951946</v>
       </c>
       <c r="I13" s="4">
-        <v>0.299886614252612</v>
+        <v>0.2159429385708277</v>
       </c>
       <c r="J13" s="4">
-        <v>1.178211804393811</v>
+        <v>1.210213934383612</v>
       </c>
       <c r="K13" s="4">
         <v>66.05025683742871</v>
@@ -4717,13 +4717,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3765713731531896</v>
+        <v>0.3769464100322782</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1465816436452366</v>
+        <v>0.1452521710373726</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1799444426269757</v>
+        <v>0.1676793984730157</v>
       </c>
       <c r="K14" s="4">
         <v>64.67745989850899</v>
@@ -4767,13 +4767,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2756421163042358</v>
+        <v>0.2728362502364238</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1727089423848585</v>
+        <v>0.1686044247820722</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2222757276873057</v>
+        <v>0.1947746632846697</v>
       </c>
       <c r="K15" s="4">
         <v>72.09873663751219</v>
@@ -4817,13 +4817,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3932554844284749</v>
+        <v>0.3934108712066841</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1695563625830095</v>
+        <v>0.1690563787896738</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1799996594589194</v>
+        <v>0.1715510423720587</v>
       </c>
       <c r="K16" s="4">
         <v>65.36645143045666</v>
@@ -5750,13 +5750,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C5" s="5">
         <v>4</v>
       </c>
       <c r="D5" s="5">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="5">
         <v>23</v>
@@ -5765,7 +5765,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" s="5">
         <v>23</v>
@@ -5882,13 +5882,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C8" s="5">
         <v>3</v>
       </c>
       <c r="D8" s="5">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
@@ -5897,7 +5897,7 @@
         <v>65</v>
       </c>
       <c r="G8" s="5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H8" s="5">
         <v>2</v>
@@ -6014,13 +6014,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
       </c>
       <c r="D11" s="5">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E11" s="5">
         <v>34</v>
@@ -6029,7 +6029,7 @@
         <v>51</v>
       </c>
       <c r="G11" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5">
         <v>34</v>
@@ -6432,16 +6432,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1642927784796811</v>
+        <v>-0.283939696655267</v>
       </c>
       <c r="O3" s="5">
         <v>83</v>
       </c>
       <c r="P3" s="4">
-        <v>1.27594369601983</v>
+        <v>1.282674049023788</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3538123706579795</v>
+        <v>0.3269764725135218</v>
       </c>
       <c r="R3" s="5">
         <v>78</v>
@@ -6491,16 +6491,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2287051283657278</v>
+        <v>-0.2162087466650391</v>
       </c>
       <c r="O4" s="5">
         <v>116</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4381863668313623</v>
+        <v>0.4384238131013009</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2479642103305954</v>
+        <v>0.2475868369714448</v>
       </c>
       <c r="R4" s="5">
         <v>115</v>
@@ -6550,16 +6550,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1506834689535106</v>
+        <v>-0.07805262609375063</v>
       </c>
       <c r="O5" s="5">
         <v>112</v>
       </c>
       <c r="P5" s="4">
-        <v>0.459296438902963</v>
+        <v>0.4600359804239603</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2274773970977599</v>
+        <v>0.2214473403517369</v>
       </c>
       <c r="R5" s="5">
         <v>112</v>
@@ -6732,16 +6732,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4109474591893756</v>
+        <v>-0.4087397332421858</v>
       </c>
       <c r="O3" s="5">
         <v>125</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8293862554076529</v>
+        <v>0.8296903134722359</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.349064333470391</v>
+        <v>0.3490466716628134</v>
       </c>
       <c r="R3" s="5">
         <v>125</v>
@@ -6791,16 +6791,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5345381396759932</v>
+        <v>-0.5070801931713902</v>
       </c>
       <c r="O4" s="5">
         <v>118</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7289035621959985</v>
+        <v>0.7308647375814833</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.383317998249511</v>
+        <v>0.3822618023110928</v>
       </c>
       <c r="R4" s="5">
         <v>117</v>
@@ -6850,16 +6850,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3186817634732127</v>
+        <v>-0.3060256481664965</v>
       </c>
       <c r="O5" s="5">
         <v>118</v>
       </c>
       <c r="P5" s="4">
-        <v>0.817533118186865</v>
+        <v>0.8179931915046239</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3910728253686231</v>
+        <v>0.3908405960814614</v>
       </c>
       <c r="R5" s="5">
         <v>118</v>
@@ -7032,22 +7032,22 @@
         <v>17</v>
       </c>
       <c r="N3" s="4">
-        <v>1.02877703237198</v>
+        <v>-0.3425778503337114</v>
       </c>
       <c r="O3" s="5">
         <v>111</v>
       </c>
       <c r="P3" s="4">
-        <v>2.51877669553776</v>
+        <v>2.067875101719155</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.343472383471488</v>
+        <v>0.3238020631604345</v>
       </c>
       <c r="R3" s="5">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S3" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7091,16 +7091,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3434277635790269</v>
+        <v>-0.2949632341903836</v>
       </c>
       <c r="O4" s="5">
         <v>114</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3276618998575161</v>
+        <v>0.3216708806089548</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2224346942637024</v>
+        <v>0.2185019115938277</v>
       </c>
       <c r="R4" s="5">
         <v>113</v>
@@ -7150,16 +7150,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.316109184758543</v>
+        <v>-0.2863323486725662</v>
       </c>
       <c r="O5" s="5">
         <v>116</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2889274881229884</v>
+        <v>0.2879741404910278</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2059740757766914</v>
+        <v>0.204624316542754</v>
       </c>
       <c r="R5" s="5">
         <v>116</v>
@@ -7332,16 +7332,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1070374288134773</v>
+        <v>-0.09407135766601016</v>
       </c>
       <c r="O3" s="5">
         <v>124</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5371763293278971</v>
+        <v>0.5385623290880551</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3798251200343382</v>
+        <v>0.3797050120355036</v>
       </c>
       <c r="R3" s="5">
         <v>124</v>
@@ -7391,16 +7391,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4348392061362967</v>
+        <v>-0.3581190663867133</v>
       </c>
       <c r="O4" s="5">
         <v>112</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5187962554989858</v>
+        <v>0.5196865354722747</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4209342099439887</v>
+        <v>0.4141268994591072</v>
       </c>
       <c r="R4" s="5">
         <v>111</v>
@@ -7450,16 +7450,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.298715712976076</v>
+        <v>-0.2610795602001943</v>
       </c>
       <c r="O5" s="5">
         <v>112</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5547545352325215</v>
+        <v>0.5572203552050055</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4083456433749695</v>
+        <v>0.4075655099546033</v>
       </c>
       <c r="R5" s="5">
         <v>111</v>
@@ -7632,16 +7632,16 @@
         <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4224707645182293</v>
+        <v>-0.298553387856451</v>
       </c>
       <c r="O3" s="5">
         <v>108</v>
       </c>
       <c r="P3" s="4">
-        <v>1.708066758882752</v>
+        <v>1.420370028013953</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7490867050740722</v>
+        <v>0.2388562390264275</v>
       </c>
       <c r="R3" s="5">
         <v>98</v>
@@ -7691,16 +7691,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.112665660820044</v>
+        <v>-0.08136645175414969</v>
       </c>
       <c r="O4" s="5">
         <v>115</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2954531537537741</v>
+        <v>0.2916507629031081</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1554569600021981</v>
+        <v>0.1523936096705392</v>
       </c>
       <c r="R4" s="5">
         <v>114</v>
@@ -7750,16 +7750,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3574979797836144</v>
+        <v>-0.3328309234326241</v>
       </c>
       <c r="O5" s="5">
         <v>117</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2865420907228443</v>
+        <v>0.2832161845087824</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1655335919389781</v>
+        <v>0.1630178381922749</v>
       </c>
       <c r="R5" s="5">
         <v>117</v>
